--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104757_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104757_W34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.551</v>
+        <v>6.8193</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7679</v>
+        <v>5.4126</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7831</v>
+        <v>1.4067</v>
       </c>
       <c r="G2" t="n">
         <v>3.2286</v>
@@ -610,13 +610,13 @@
         <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3208</v>
+        <v>-0.4109</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2559</v>
+        <v>-0.6112</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5767</v>
+        <v>0.2003</v>
       </c>
       <c r="V2" t="n">
         <v>2.4082</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8292</v>
+        <v>5.2613</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6448</v>
+        <v>4.7633</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1844</v>
+        <v>0.498</v>
       </c>
       <c r="G3" t="n">
         <v>4.7149</v>
@@ -688,13 +688,13 @@
         <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.016</v>
+        <v>-1.5839</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9061</v>
+        <v>-0.7877</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1099</v>
+        <v>-0.7962</v>
       </c>
       <c r="V3" t="n">
         <v>3.2684</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2495</v>
+        <v>2.8698</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1509</v>
+        <v>4.6771</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9014</v>
+        <v>-1.8073</v>
       </c>
       <c r="G4" t="n">
         <v>4.6115</v>
@@ -766,13 +766,13 @@
         <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3228</v>
+        <v>-0.7025</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1165</v>
+        <v>-0.5903</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2063</v>
+        <v>-0.1122</v>
       </c>
       <c r="V4" t="n">
         <v>-1.9497</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1435</v>
+        <v>2.3804</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0368</v>
+        <v>1.2737</v>
       </c>
       <c r="F5" t="n">
         <v>1.1067</v>
@@ -844,10 +844,10 @@
         <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2308</v>
+        <v>-0.9939</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7667</v>
+        <v>-0.5298</v>
       </c>
       <c r="U5" t="n">
         <v>-0.464</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.488</v>
+        <v>0.9969</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1914</v>
+        <v>0.4807</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2967</v>
+        <v>0.5162</v>
       </c>
       <c r="G6" t="n">
         <v>1.339</v>
@@ -922,13 +922,13 @@
         <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7827</v>
+        <v>-1.2738</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0217</v>
+        <v>0.311</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.8043</v>
+        <v>-1.5848</v>
       </c>
       <c r="V6" t="n">
         <v>0.9317</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4217</v>
+        <v>-0.2713</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.929</v>
+        <v>-0.774</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5073</v>
+        <v>0.5027</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.675</v>
+        <v>-0.5777</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0433</v>
+        <v>0.4649</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6317</v>
+        <v>-1.0426</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7896</v>
+        <v>-0.6807</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0345</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7896</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1146</v>
+        <v>0.103</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0433</v>
+        <v>0.4305</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1579</v>
+        <v>-0.3275</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2533</v>
+        <v>-0.5342</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1394</v>
+        <v>-0.251</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3927</v>
+        <v>-0.2832</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.5228</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0109</v>
+        <v>-0.8106</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3772</v>
+        <v>0.2878</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5777</v>
+        <v>-0.675</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4649</v>
+        <v>-0.0433</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0426</v>
+        <v>-0.6317</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6807</v>
+        <v>-0.7896</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0345</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.7896</v>
       </c>
       <c r="M8" t="n">
-        <v>0.103</v>
+        <v>0.1146</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4305</v>
+        <v>-0.0433</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3275</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6829</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6829</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8966</v>
+        <v>0.1522</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4879</v>
+        <v>-0.021</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4087</v>
+        <v>0.1732</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1578</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1578</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9397</v>
+        <v>-0.64</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1197</v>
+        <v>0.1172</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.82</v>
+        <v>-0.7573</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6983</v>
@@ -1156,13 +1156,13 @@
         <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6966</v>
+        <v>-0.397</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2091</v>
+        <v>0.0278</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4875</v>
+        <v>-0.4248</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2513</v>
+        <v>-1.0183</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3318</v>
+        <v>-1.1992</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5831</v>
+        <v>0.1809</v>
       </c>
       <c r="G10" t="n">
-        <v>1.66</v>
+        <v>-1.4554</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1772</v>
+        <v>-0.6182</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4828</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4816</v>
+        <v>-1.4011</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6755</v>
+        <v>-0.3727</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1939</v>
+        <v>-1.0284</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1784</v>
+        <v>-0.0543</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5018</v>
+        <v>-0.2455</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6766</v>
+        <v>0.1912</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6829</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3658</v>
+        <v>-1.5934</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6829</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6836</v>
+        <v>-1.2866</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4182</v>
+        <v>-0.3836</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2654</v>
+        <v>-0.903</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5447</v>
+        <v>2.1789</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6342</v>
+        <v>2.1789</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7987</v>
+        <v>-1.2199</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7914</v>
+        <v>0.3318</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0073</v>
+        <v>-1.5517</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4554</v>
+        <v>1.66</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6182</v>
+        <v>1.1772</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8372000000000001</v>
+        <v>0.4828</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4011</v>
+        <v>0.4816</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3727</v>
+        <v>0.6755</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0284</v>
+        <v>-0.1939</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0543</v>
+        <v>1.1784</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2455</v>
+        <v>0.5018</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1912</v>
+        <v>0.6766</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4553</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.5934</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1382</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.067</v>
+        <v>-1.6523</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9758</v>
+        <v>-0.4182</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0912</v>
+        <v>-1.2341</v>
       </c>
       <c r="V11" t="n">
-        <v>2.1789</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1789</v>
+        <v>1.6342</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.834</v>
+        <v>-3.3572</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4579</v>
+        <v>-2.0337</v>
       </c>
       <c r="F12" t="n">
-        <v>1.624</v>
+        <v>-1.3235</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3985</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2781</v>
+        <v>-0.4854</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6766</v>
+        <v>-0.2902</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4004</v>
+        <v>-0.7352</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1067</v>
+        <v>-0.7724</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5071</v>
+        <v>0.0372</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0019</v>
+        <v>-0.0405</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1715</v>
+        <v>0.287</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1695</v>
+        <v>-0.3275</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.5039</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.6421</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1382</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4555</v>
+        <v>-0.9685</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1862</v>
+        <v>-0.1604</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6417</v>
+        <v>-0.8082</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.387</v>
+        <v>-0.7025</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2292</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1578</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4757</v>
+        <v>-3.3915</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1521</v>
+        <v>-4.5764</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3235</v>
+        <v>1.1848</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.3985</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4854</v>
+        <v>0.2781</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2902</v>
+        <v>-0.6766</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7352</v>
+        <v>-0.4004</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7724</v>
+        <v>0.1067</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0372</v>
+        <v>-0.5071</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0405</v>
+        <v>0.0019</v>
       </c>
       <c r="N13" t="n">
-        <v>0.287</v>
+        <v>0.1715</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3275</v>
+        <v>-0.1695</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9105</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1382</v>
+        <v>-3.6421</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2276</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.087</v>
+        <v>-0.1021</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2788</v>
+        <v>-0.3046</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8082</v>
+        <v>0.2025</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.7025</v>
+        <v>-0.387</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.2292</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.7025</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.906499999999998</v>
+        <v>7.906699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>7.6626</v>
+        <v>7.6625</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2441</v>
+        <v>0.2440000000000002</v>
       </c>
       <c r="G14" t="n">
         <v>14.4175</v>
@@ -1546,16 +1546,16 @@
         <v>11.3817</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.753499999999999</v>
+        <v>-9.753500000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.7189</v>
+        <v>-3.719</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.0344</v>
+        <v>-6.0345</v>
       </c>
       <c r="V14" t="n">
-        <v>5.518900000000001</v>
+        <v>5.5189</v>
       </c>
       <c r="W14" t="n">
         <v>12.2282</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. TILLIE</t>
+          <t>A. RUBIT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4393</v>
+        <v>2.0753</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1387</v>
+        <v>3.131</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6994</v>
+        <v>-1.0557</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.3187</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.866</v>
+        <v>1.0845</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5473</v>
+        <v>-0.5406</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8875</v>
+        <v>1.3593</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.2623</v>
+        <v>1.5159</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1498</v>
+        <v>-0.1566</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2062</v>
+        <v>-0.8154</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6037</v>
+        <v>-0.4314</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6025</v>
+        <v>-0.384</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5934</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5934</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5696</v>
+        <v>1.325</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2512</v>
+        <v>0.7521</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3184</v>
+        <v>0.5729</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.405</v>
+        <v>-0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.405</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>J. WEBB III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3283</v>
+        <v>1.7086</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3095</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0188</v>
+        <v>0.9369</v>
       </c>
       <c r="G16" t="n">
-        <v>0.379</v>
+        <v>0.6401</v>
       </c>
       <c r="H16" t="n">
-        <v>1.514</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1351</v>
+        <v>0.6317</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5626</v>
+        <v>0.0517</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4716</v>
+        <v>0.0517</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.909</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1836</v>
+        <v>0.5884</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0424</v>
+        <v>-0.0433</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.226</v>
+        <v>0.6317</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3658</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3658</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3363</v>
+        <v>-0.4762</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2524</v>
+        <v>-0.3695</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0838</v>
+        <v>-0.1067</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.387</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8603</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. WEBB III</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4647</v>
+        <v>1.339</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6533</v>
+        <v>1.0066</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8114</v>
+        <v>0.3324</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6401</v>
+        <v>0.379</v>
       </c>
       <c r="H17" t="n">
-        <v>0.008399999999999999</v>
+        <v>1.514</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6317</v>
+        <v>-1.1351</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0517</v>
+        <v>0.5626</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0517</v>
+        <v>1.4716</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.909</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5884</v>
+        <v>-0.1836</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0433</v>
+        <v>0.0424</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6317</v>
+        <v>-0.226</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4553</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4553</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7201</v>
+        <v>1.347</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4879</v>
+        <v>0.9495</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2322</v>
+        <v>0.3975</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0895</v>
+        <v>-0.387</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0895</v>
+        <v>0.8603</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RUBIT</t>
+          <t>K. TILLIE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4587</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4203</v>
+        <v>2.7174</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9616</v>
+        <v>-1.7935</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5439000000000001</v>
+        <v>-1.3187</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0845</v>
+        <v>-2.866</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5406</v>
+        <v>1.5473</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3593</v>
+        <v>0.8875</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5159</v>
+        <v>-2.2623</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1566</v>
+        <v>3.1498</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8154</v>
+        <v>-2.2062</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4314</v>
+        <v>-0.6037</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.384</v>
+        <v>-1.6025</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1382</v>
+        <v>1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2276</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3658</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7084</v>
+        <v>2.0542</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0414</v>
+        <v>1.8298</v>
       </c>
       <c r="U18" t="n">
-        <v>0.667</v>
+        <v>0.2243</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9317</v>
+        <v>-1.405</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2472</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1789</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>N. DJEDOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0331</v>
+        <v>0.7851</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6985</v>
+        <v>-1.3074</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7315</v>
+        <v>2.0925</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3747</v>
+        <v>-0.7627</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0494</v>
+        <v>-0.4365</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.3253</v>
+        <v>-0.3262</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.916</v>
+        <v>-1.2673</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2241</v>
+        <v>-0.321</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1401</v>
+        <v>-0.9463</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4587</v>
+        <v>0.5046</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2734</v>
+        <v>-0.1155</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1852</v>
+        <v>0.6201</v>
       </c>
       <c r="P19" t="n">
         <v>1.3658</v>
@@ -1936,28 +1936,28 @@
         <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.655</v>
+        <v>0.0242</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.098</v>
+        <v>-0.1979</v>
       </c>
       <c r="U19" t="n">
-        <v>0.753</v>
+        <v>0.2221</v>
       </c>
       <c r="V19" t="n">
-        <v>0.387</v>
+        <v>0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3155</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>0.07140000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. DJEDOVIC</t>
+          <t>J. COBBS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1381</v>
+        <v>0.6703</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1365</v>
+        <v>-0.549</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9984</v>
+        <v>1.2193</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7627</v>
+        <v>0.2653</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4365</v>
+        <v>0.7212</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3262</v>
+        <v>-0.4558</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2673</v>
+        <v>0.4085</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.321</v>
+        <v>1.1236</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9463</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5046</v>
+        <v>-0.1432</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1155</v>
+        <v>-0.4025</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6201</v>
+        <v>0.2593</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3658</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3658</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.899</v>
+        <v>0.4749</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.027</v>
+        <v>0.2505</v>
       </c>
       <c r="U20" t="n">
-        <v>0.128</v>
+        <v>0.2243</v>
       </c>
       <c r="V20" t="n">
         <v>0.1578</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. COBBS</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1831</v>
+        <v>0.1375</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4966</v>
+        <v>-0.3431</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3134</v>
+        <v>0.4806</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2653</v>
+        <v>-2.3747</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7212</v>
+        <v>-0.0494</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4558</v>
+        <v>-2.3253</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4085</v>
+        <v>-0.916</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1236</v>
+        <v>0.2241</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-1.1401</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1432</v>
+        <v>-1.4587</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4025</v>
+        <v>-0.2734</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2593</v>
+        <v>-1.1852</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2276</v>
+        <v>1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3658</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1382</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3786</v>
+        <v>0.7594</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.697</v>
+        <v>0.2574</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3184</v>
+        <v>0.5021</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1578</v>
+        <v>0.387</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1578</v>
+        <v>0.3155</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1866</v>
+        <v>-0.6777</v>
       </c>
       <c r="E22" t="n">
-        <v>2.4418</v>
+        <v>1.7311</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6285</v>
+        <v>-2.4089</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4798</v>
@@ -2170,13 +2170,13 @@
         <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5906</v>
+        <v>1.0995</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6022</v>
+        <v>0.8915</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0116</v>
+        <v>0.208</v>
       </c>
       <c r="V22" t="n">
         <v>0.1578</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.953</v>
+        <v>-2.0471</v>
       </c>
       <c r="E23" t="n">
         <v>-2.7205</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7674</v>
+        <v>0.6733</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5047</v>
@@ -2248,13 +2248,13 @@
         <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>0.007</v>
+        <v>-0.0871</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2788</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2858</v>
+        <v>0.1917</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1877</v>
+        <v>-2.6966</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1582</v>
+        <v>0.5525</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0295</v>
+        <v>-3.249</v>
       </c>
       <c r="G24" t="n">
         <v>-0.07149999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7456</v>
+        <v>1.2367</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0283</v>
+        <v>0.6824</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7739</v>
+        <v>0.5543</v>
       </c>
       <c r="V24" t="n">
         <v>-2.7237</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4166</v>
+        <v>-4.6951</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5222</v>
+        <v>-2.7067</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8944</v>
+        <v>-1.9885</v>
       </c>
       <c r="G25" t="n">
         <v>-4.1267</v>
@@ -2404,13 +2404,13 @@
         <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8695</v>
+        <v>0.5909</v>
       </c>
       <c r="T25" t="n">
-        <v>1.551</v>
+        <v>0.3665</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3184</v>
+        <v>0.2243</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9317</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.5656</v>
+        <v>-5.4299</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.3175</v>
+        <v>-2.37</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.2481</v>
+        <v>-3.0599</v>
       </c>
       <c r="G26" t="n">
         <v>-4.6073</v>
@@ -2482,13 +2482,13 @@
         <v>1.3658</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2693</v>
+        <v>1.405</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0468</v>
+        <v>0.9008</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3161</v>
+        <v>0.5043</v>
       </c>
       <c r="V26" t="n">
         <v>-1.0895</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.906600000000001</v>
+        <v>-7.906700000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.08639999999999937</v>
+        <v>-0.0864000000000007</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.8206</v>
+        <v>-7.820500000000001</v>
       </c>
       <c r="G27" t="n">
         <v>-14.4178</v>
@@ -2560,13 +2560,13 @@
         <v>13.658</v>
       </c>
       <c r="S27" t="n">
-        <v>9.753599999999999</v>
+        <v>9.753499999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>6.0344</v>
+        <v>6.034300000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>3.719</v>
+        <v>3.7191</v>
       </c>
       <c r="V27" t="n">
         <v>-5.5187</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104757_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104757_W34.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.709599999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104757_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-12.386</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
